--- a/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -951,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>157000</v>
+        <v>128200</v>
       </c>
       <c r="E14" s="3">
         <v>-24500</v>
@@ -1050,7 +1050,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3576300</v>
+        <v>3519900</v>
       </c>
       <c r="E17" s="3">
         <v>2669000</v>
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>259700</v>
+        <v>316100</v>
       </c>
       <c r="E18" s="3">
         <v>130800</v>
@@ -1152,7 +1152,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-15000</v>
+        <v>121200</v>
       </c>
       <c r="E20" s="3">
         <v>-23500</v>
@@ -1194,7 +1194,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>387600</v>
+        <v>580200</v>
       </c>
       <c r="E21" s="3">
         <v>251200</v>
@@ -1278,7 +1278,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>162000</v>
+        <v>354600</v>
       </c>
       <c r="E23" s="3">
         <v>10600</v>
@@ -1404,7 +1404,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>146500</v>
+        <v>339100</v>
       </c>
       <c r="E26" s="3">
         <v>-16200</v>
@@ -1446,7 +1446,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>130900</v>
+        <v>323500</v>
       </c>
       <c r="E27" s="3">
         <v>-38200</v>
@@ -1656,7 +1656,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>15000</v>
+        <v>-121200</v>
       </c>
       <c r="E32" s="3">
         <v>23500</v>
@@ -1698,7 +1698,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>130900</v>
+        <v>323500</v>
       </c>
       <c r="E33" s="3">
         <v>-38200</v>
@@ -1782,7 +1782,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>130900</v>
+        <v>323500</v>
       </c>
       <c r="E35" s="3">
         <v>-38200</v>
@@ -3436,7 +3436,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>130900</v>
+        <v>323500</v>
       </c>
       <c r="E81" s="3">
         <v>-38200</v>

--- a/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>ATI</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4173700</v>
+      </c>
+      <c r="E8" s="3">
         <v>3836000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2799800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2982100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4122500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4046600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3525100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3134600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3719600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4223400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4043500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4666900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4812300</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3347400</v>
+      </c>
+      <c r="E9" s="3">
         <v>3121800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2466600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2689300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3484700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3416300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3028100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2911800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3659300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3847000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3782300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8376500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4075500</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>826300</v>
+      </c>
+      <c r="E10" s="3">
         <v>714200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>333200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>292800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>637800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>630300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>497000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>222800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>60300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>376400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>261200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-3709600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>736800</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E14" s="3">
         <v>128200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-24500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1418400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>39400</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>151400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>523800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>190900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>67500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3519900</v>
+        <v>3707300</v>
       </c>
       <c r="E17" s="3">
-        <v>2669000</v>
+        <v>3547500</v>
       </c>
       <c r="F17" s="3">
+        <v>2733900</v>
+      </c>
+      <c r="G17" s="3">
         <v>4308700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3791300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3684500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3427500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3676400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4089000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4117300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4134800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4363000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4398500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>316100</v>
+        <v>466400</v>
       </c>
       <c r="E18" s="3">
-        <v>130800</v>
+        <v>288500</v>
       </c>
       <c r="F18" s="3">
+        <v>65900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1326600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>331200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>362100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>97600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-541800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-369400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>106100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-91300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>303900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>413800</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>121200</v>
+        <v>-157700</v>
       </c>
       <c r="E20" s="3">
-        <v>-23500</v>
+        <v>231500</v>
       </c>
       <c r="F20" s="3">
+        <v>264200</v>
+      </c>
+      <c r="G20" s="3">
         <v>-62600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-12300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-49200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>58600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>73200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>95700</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>580200</v>
+        <v>454800</v>
       </c>
       <c r="E21" s="3">
-        <v>251200</v>
+        <v>662900</v>
       </c>
       <c r="F21" s="3">
+        <v>474000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1245900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>486300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>506200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>209200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-312900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-176700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>288100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>101100</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>683900</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>82700</v>
+        <v>13500</v>
       </c>
       <c r="E22" s="3">
+        <v>165400</v>
+      </c>
+      <c r="F22" s="3">
         <v>96700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>92700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>93600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>102100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>134900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>250800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>111400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>109800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>66000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>144800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>187400</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>295200</v>
+      </c>
+      <c r="E23" s="3">
         <v>354600</v>
       </c>
-      <c r="E23" s="3">
-        <v>10600</v>
-      </c>
       <c r="F23" s="3">
+        <v>233400</v>
+      </c>
+      <c r="G23" s="3">
         <v>-1481900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>241600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>247700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-86500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-734000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-478000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-154800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>232300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>322100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="E24" s="3">
         <v>15500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>77700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-28500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-106900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-112100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-8700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-63600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>72400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>110400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>423400</v>
+      </c>
+      <c r="E26" s="3">
         <v>339100</v>
       </c>
-      <c r="E26" s="3">
-        <v>-16200</v>
-      </c>
       <c r="F26" s="3">
+        <v>206600</v>
+      </c>
+      <c r="G26" s="3">
         <v>-1559600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>270100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>242600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-83800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-627100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-365900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-91200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>159900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>211700</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>410800</v>
+      </c>
+      <c r="E27" s="3">
         <v>323500</v>
       </c>
-      <c r="E27" s="3">
-        <v>-38200</v>
-      </c>
       <c r="F27" s="3">
+        <v>184600</v>
+      </c>
+      <c r="G27" s="3">
         <v>-1572600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>257600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>228300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-96000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-640900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-377900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-98800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>150500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>202900</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1538,36 +1598,39 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-5900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>4100</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>252800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>7900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>11400</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-121200</v>
+        <v>157700</v>
       </c>
       <c r="E32" s="3">
-        <v>23500</v>
+        <v>-231500</v>
       </c>
       <c r="F32" s="3">
+        <v>-264200</v>
+      </c>
+      <c r="G32" s="3">
         <v>62600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>12300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>49200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-58600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-73200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-95700</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>410800</v>
+      </c>
+      <c r="E33" s="3">
         <v>323500</v>
       </c>
-      <c r="E33" s="3">
-        <v>-38200</v>
-      </c>
       <c r="F33" s="3">
+        <v>184600</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1572600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>257600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>222400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-91900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-640900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-377900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>154000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>158400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>214300</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>410800</v>
+      </c>
+      <c r="E35" s="3">
         <v>323500</v>
       </c>
-      <c r="E35" s="3">
-        <v>-38200</v>
-      </c>
       <c r="F35" s="3">
+        <v>184600</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1572600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>257600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>222400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-91900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-640900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-377900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>154000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>158400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>214300</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,260 +1986,279 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>329800</v>
+      </c>
+      <c r="E41" s="3">
         <v>164900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
+        <v>687700</v>
+      </c>
+      <c r="G41" s="3">
+        <v>158200</v>
+      </c>
+      <c r="H41" s="3">
+        <v>190800</v>
+      </c>
+      <c r="I41" s="3">
+        <v>264400</v>
+      </c>
+      <c r="J41" s="3">
+        <v>140200</v>
+      </c>
+      <c r="K41" s="3">
+        <v>164100</v>
+      </c>
+      <c r="L41" s="3">
+        <v>149300</v>
+      </c>
+      <c r="M41" s="3">
+        <v>267700</v>
+      </c>
+      <c r="N41" s="3">
+        <v>1025200</v>
+      </c>
+      <c r="O41" s="3">
         <v>222800</v>
       </c>
-      <c r="F41" s="3">
-        <v>158200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>190800</v>
-      </c>
-      <c r="H41" s="3">
-        <v>264400</v>
-      </c>
-      <c r="I41" s="3">
-        <v>140200</v>
-      </c>
-      <c r="J41" s="3">
-        <v>164100</v>
-      </c>
-      <c r="K41" s="3">
-        <v>149300</v>
-      </c>
-      <c r="L41" s="3">
-        <v>267700</v>
-      </c>
-      <c r="M41" s="3">
-        <v>1025200</v>
-      </c>
-      <c r="N41" s="3">
-        <v>222800</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>339600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>414100</v>
+      </c>
+      <c r="E42" s="3">
         <v>419100</v>
       </c>
-      <c r="E42" s="3">
-        <v>464900</v>
-      </c>
-      <c r="F42" s="3">
+      <c r="F42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="3">
         <v>487700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>300000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>117600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>65500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>82200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>41000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>684100</v>
+      </c>
+      <c r="E43" s="3">
         <v>643300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>523900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>384700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>592600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>579000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>545300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>452100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>603600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>528200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>613300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>709100</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1247500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1195700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1046300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>997100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1155300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1211100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1176100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1037000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1271600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1472800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1322100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1536600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1384300</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E45" s="3">
         <v>53400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>64300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>74600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>52700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>47800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>45500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>129800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>73700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>111800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>95500</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2737700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2476400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2306700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2066000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2303000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2246700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1915700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1766500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1867600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2482100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2950800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2510600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2569500</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2194,93 +2298,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1665900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1549100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1528500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1469200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2501800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2475000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2495700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2498900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2928200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2961800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2874100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2559900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2368800</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>278300</v>
+      </c>
+      <c r="E49" s="3">
         <v>285700</v>
       </c>
-      <c r="E49" s="3">
-        <v>293800</v>
-      </c>
       <c r="F49" s="3">
+        <v>227900</v>
+      </c>
+      <c r="G49" s="3">
         <v>328600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>622100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>664400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>669400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>790100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>809700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>948900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>880700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>740100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>737700</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>303200</v>
+      </c>
+      <c r="E52" s="3">
         <v>134400</v>
       </c>
-      <c r="E52" s="3">
-        <v>156200</v>
-      </c>
       <c r="F52" s="3">
+        <v>222100</v>
+      </c>
+      <c r="G52" s="3">
         <v>171100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>207700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>115700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>104600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>114500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>146200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>189800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>192900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>802900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>370900</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4985100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4445600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4285200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4034900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5634600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5501800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5185400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5170000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5751700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6582600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6898500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6247800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6046900</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>524800</v>
+      </c>
+      <c r="E57" s="3">
         <v>553300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>375500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>290600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>521200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>498800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>420100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>294300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>380800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>556700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>471800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>499900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>490700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E58" s="3">
         <v>41700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>131300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>105100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>419900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>17100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>27300</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>420400</v>
+      </c>
+      <c r="E59" s="3">
         <v>368900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>349600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>344900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>316500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>331500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>282400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>309300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>301800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>385400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>319300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>685000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>343800</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>977100</v>
+      </c>
+      <c r="E60" s="3">
         <v>963900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>856400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>653300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>849200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>836900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>712600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>708700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>686500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>959900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1211000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>871500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>861800</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2147700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1706300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1711600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1550000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1387400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1535500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1530600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1771900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1491800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1509100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1527400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1463000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1482000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>379800</v>
+      </c>
+      <c r="E62" s="3">
         <v>618200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>884500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1190200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1204800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1137800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1097700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1244600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1376900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1392200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1165400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1436100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1131500</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3612100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3399700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3599600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3513800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3544500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3616100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3446000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3814800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3668900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3984200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4004300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3768200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3571600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-70100</v>
+      </c>
+      <c r="E72" s="3">
         <v>176900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>72700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>106500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1679300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1422000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1184300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1277100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1945900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2398900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2490100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2427600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2361500</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1373000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1045900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>685600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>521100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2090100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1885700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1739400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1355200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2082800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2598400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2894200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2479600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2475300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>410800</v>
+      </c>
+      <c r="E81" s="3">
         <v>323500</v>
       </c>
-      <c r="E81" s="3">
-        <v>-38200</v>
-      </c>
       <c r="F81" s="3">
+        <v>184600</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1572600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>257600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>222400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-91900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-640900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-377900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>154000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>158400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>214300</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E83" s="3">
         <v>142900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>143900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>143300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>151100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>156400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>160800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>170300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>189900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>176800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>189900</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>174400</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>85900</v>
+      </c>
+      <c r="E89" s="3">
         <v>224900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>166900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>230100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>392800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-43700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>131400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>55900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>368400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>427500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>296800</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-130900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-152600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-136500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-168400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-139200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-122700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-202200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-144600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-225700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-612700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-382000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-278200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-193200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-126700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-77300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-128700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>81700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-145100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-119600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-145100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-316200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11000</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-624700</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4012,26 +4245,29 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-25800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-66500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-77100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-76900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-76500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-74700</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,51 +4397,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>267200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-201900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>103000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>116900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-203000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>323500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-106000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-497000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>364800</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>276200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4233,55 +4481,61 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>159900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-103700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>41800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>155100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>108800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>240400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-88000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>79800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-119700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-757300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>722200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-76000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-51700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>ATI</t>
   </si>
@@ -662,7 +662,9 @@
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -684,10 +686,10 @@
         <v>45291</v>
       </c>
       <c r="E7" s="2">
-        <v>44926</v>
+        <v>44927</v>
       </c>
       <c r="F7" s="2">
-        <v>44561</v>
+        <v>44563</v>
       </c>
       <c r="G7" s="2">
         <v>44196</v>
@@ -771,19 +773,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3347400</v>
+        <v>3360800</v>
       </c>
       <c r="E9" s="3">
         <v>3121800</v>
       </c>
       <c r="F9" s="3">
-        <v>2466600</v>
+        <v>2465800</v>
       </c>
       <c r="G9" s="3">
         <v>2689300</v>
       </c>
       <c r="H9" s="3">
-        <v>3484700</v>
+        <v>3484500</v>
       </c>
       <c r="I9" s="3">
         <v>3416300</v>
@@ -816,19 +818,19 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>826300</v>
+        <v>812900</v>
       </c>
       <c r="E10" s="3">
         <v>714200</v>
       </c>
       <c r="F10" s="3">
-        <v>333200</v>
+        <v>334000</v>
       </c>
       <c r="G10" s="3">
         <v>292800</v>
       </c>
       <c r="H10" s="3">
-        <v>637800</v>
+        <v>638000</v>
       </c>
       <c r="I10" s="3">
         <v>630300</v>
@@ -879,26 +881,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F12" s="3">
+        <v>20000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>14800</v>
+      </c>
+      <c r="H12" s="3">
+        <v>20200</v>
+      </c>
+      <c r="I12" s="3">
+        <v>24900</v>
+      </c>
+      <c r="J12" s="3">
+        <v>14700</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -970,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>31800</v>
+        <v>18100</v>
       </c>
       <c r="E14" s="3">
-        <v>128200</v>
+        <v>128000</v>
       </c>
       <c r="F14" s="3">
-        <v>-24500</v>
+        <v>38300</v>
       </c>
       <c r="G14" s="3">
-        <v>1418400</v>
+        <v>1432900</v>
       </c>
       <c r="H14" s="3">
-        <v>39400</v>
+        <v>-46100</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-17200</v>
       </c>
       <c r="J14" s="3">
-        <v>151400</v>
+        <v>150900</v>
       </c>
       <c r="K14" s="3">
         <v>523800</v>
@@ -1015,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>120600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>123400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>125400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>151300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>151100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>156400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>145200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3707300</v>
+        <v>3768600</v>
       </c>
       <c r="E17" s="3">
-        <v>3547500</v>
+        <v>3280900</v>
       </c>
       <c r="F17" s="3">
-        <v>2733900</v>
+        <v>2432700</v>
       </c>
       <c r="G17" s="3">
-        <v>4308700</v>
+        <v>2935000</v>
       </c>
       <c r="H17" s="3">
-        <v>3791300</v>
+        <v>3825300</v>
       </c>
       <c r="I17" s="3">
-        <v>3684500</v>
+        <v>3718400</v>
       </c>
       <c r="J17" s="3">
-        <v>3427500</v>
+        <v>3330400</v>
       </c>
       <c r="K17" s="3">
         <v>3676400</v>
@@ -1121,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>466400</v>
+        <v>405100</v>
       </c>
       <c r="E18" s="3">
-        <v>288500</v>
+        <v>555100</v>
       </c>
       <c r="F18" s="3">
-        <v>65900</v>
+        <v>367100</v>
       </c>
       <c r="G18" s="3">
-        <v>-1326600</v>
+        <v>47100</v>
       </c>
       <c r="H18" s="3">
-        <v>331200</v>
+        <v>297200</v>
       </c>
       <c r="I18" s="3">
-        <v>362100</v>
+        <v>328200</v>
       </c>
       <c r="J18" s="3">
-        <v>97600</v>
+        <v>194700</v>
       </c>
       <c r="K18" s="3">
         <v>-541800</v>
@@ -1185,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-157700</v>
+        <v>-1000</v>
       </c>
       <c r="E20" s="3">
-        <v>231500</v>
+        <v>-14900</v>
       </c>
       <c r="F20" s="3">
-        <v>264200</v>
+        <v>-1500</v>
       </c>
       <c r="G20" s="3">
-        <v>-62600</v>
+        <v>1700</v>
       </c>
       <c r="H20" s="3">
-        <v>4000</v>
+        <v>7800</v>
       </c>
       <c r="I20" s="3">
-        <v>-12300</v>
+        <v>-3300</v>
       </c>
       <c r="J20" s="3">
-        <v>-49200</v>
+        <v>-3500</v>
       </c>
       <c r="K20" s="3">
         <v>58600</v>
@@ -1230,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>454800</v>
+        <v>526700</v>
       </c>
       <c r="E21" s="3">
-        <v>662900</v>
+        <v>693400</v>
       </c>
       <c r="F21" s="3">
-        <v>474000</v>
+        <v>494000</v>
       </c>
       <c r="G21" s="3">
-        <v>-1245900</v>
+        <v>196700</v>
       </c>
       <c r="H21" s="3">
-        <v>486300</v>
+        <v>440500</v>
       </c>
       <c r="I21" s="3">
-        <v>506200</v>
+        <v>487900</v>
       </c>
       <c r="J21" s="3">
-        <v>209200</v>
+        <v>343400</v>
       </c>
       <c r="K21" s="3">
         <v>-312900</v>
@@ -1275,19 +1277,19 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>13500</v>
+        <v>105800</v>
       </c>
       <c r="E22" s="3">
-        <v>165400</v>
+        <v>92100</v>
       </c>
       <c r="F22" s="3">
-        <v>96700</v>
+        <v>97600</v>
       </c>
       <c r="G22" s="3">
-        <v>92700</v>
+        <v>96100</v>
       </c>
       <c r="H22" s="3">
-        <v>93600</v>
+        <v>104900</v>
       </c>
       <c r="I22" s="3">
         <v>102100</v>
@@ -1332,7 +1334,7 @@
         <v>-1481900</v>
       </c>
       <c r="H23" s="3">
-        <v>241600</v>
+        <v>236500</v>
       </c>
       <c r="I23" s="3">
         <v>247700</v>
@@ -1380,10 +1382,10 @@
         <v>-28500</v>
       </c>
       <c r="I24" s="3">
-        <v>5100</v>
+        <v>11000</v>
       </c>
       <c r="J24" s="3">
-        <v>-2700</v>
+        <v>-6800</v>
       </c>
       <c r="K24" s="3">
         <v>-106900</v>
@@ -1467,13 +1469,13 @@
         <v>-1559600</v>
       </c>
       <c r="H26" s="3">
-        <v>270100</v>
+        <v>265000</v>
       </c>
       <c r="I26" s="3">
-        <v>242600</v>
+        <v>236700</v>
       </c>
       <c r="J26" s="3">
-        <v>-83800</v>
+        <v>-79700</v>
       </c>
       <c r="K26" s="3">
         <v>-627100</v>
@@ -1512,13 +1514,13 @@
         <v>-1572600</v>
       </c>
       <c r="H27" s="3">
-        <v>257600</v>
+        <v>252500</v>
       </c>
       <c r="I27" s="3">
-        <v>228300</v>
+        <v>222400</v>
       </c>
       <c r="J27" s="3">
-        <v>-96000</v>
+        <v>-91900</v>
       </c>
       <c r="K27" s="3">
         <v>-640900</v>
@@ -1589,26 +1591,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-5900</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1725,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>157700</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="3">
-        <v>-231500</v>
+        <v>14900</v>
       </c>
       <c r="F32" s="3">
-        <v>-264200</v>
+        <v>1500</v>
       </c>
       <c r="G32" s="3">
-        <v>62600</v>
+        <v>-1700</v>
       </c>
       <c r="H32" s="3">
-        <v>-4000</v>
+        <v>-7800</v>
       </c>
       <c r="I32" s="3">
-        <v>12300</v>
+        <v>3300</v>
       </c>
       <c r="J32" s="3">
-        <v>49200</v>
+        <v>3500</v>
       </c>
       <c r="K32" s="3">
         <v>-58600</v>
@@ -1782,7 +1784,7 @@
         <v>-1572600</v>
       </c>
       <c r="H33" s="3">
-        <v>257600</v>
+        <v>252500</v>
       </c>
       <c r="I33" s="3">
         <v>222400</v>
@@ -1872,7 +1874,7 @@
         <v>-1572600</v>
       </c>
       <c r="H35" s="3">
-        <v>257600</v>
+        <v>252500</v>
       </c>
       <c r="I35" s="3">
         <v>222400</v>
@@ -1913,10 +1915,10 @@
         <v>45291</v>
       </c>
       <c r="E38" s="2">
-        <v>44926</v>
+        <v>44927</v>
       </c>
       <c r="F38" s="2">
-        <v>44561</v>
+        <v>44563</v>
       </c>
       <c r="G38" s="2">
         <v>44196</v>
@@ -1993,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>329800</v>
+        <v>743900</v>
       </c>
       <c r="E41" s="3">
-        <v>164900</v>
+        <v>584000</v>
       </c>
       <c r="F41" s="3">
         <v>687700</v>
       </c>
       <c r="G41" s="3">
-        <v>158200</v>
+        <v>645900</v>
       </c>
       <c r="H41" s="3">
-        <v>190800</v>
+        <v>490800</v>
       </c>
       <c r="I41" s="3">
-        <v>264400</v>
+        <v>382000</v>
       </c>
       <c r="J41" s="3">
-        <v>140200</v>
+        <v>141600</v>
       </c>
       <c r="K41" s="3">
         <v>164100</v>
@@ -2038,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>414100</v>
+        <v>700</v>
       </c>
       <c r="E42" s="3">
-        <v>419100</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
+        <v>1400</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>487700</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>117600</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>65500</v>
@@ -2173,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>62200</v>
+        <v>600</v>
       </c>
       <c r="E45" s="3">
-        <v>53400</v>
+        <v>15300</v>
       </c>
       <c r="F45" s="3">
-        <v>48800</v>
+        <v>7700</v>
       </c>
       <c r="G45" s="3">
-        <v>38300</v>
+        <v>4400</v>
       </c>
       <c r="H45" s="3">
-        <v>64300</v>
+        <v>4400</v>
       </c>
       <c r="I45" s="3">
-        <v>74600</v>
+        <v>12900</v>
       </c>
       <c r="J45" s="3">
-        <v>52700</v>
+        <v>10700</v>
       </c>
       <c r="K45" s="3">
         <v>47800</v>
@@ -2262,26 +2264,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2320,7 +2322,7 @@
         <v>1469200</v>
       </c>
       <c r="H48" s="3">
-        <v>2501800</v>
+        <v>2450100</v>
       </c>
       <c r="I48" s="3">
         <v>2475000</v>
@@ -2359,7 +2361,7 @@
         <v>285700</v>
       </c>
       <c r="F49" s="3">
-        <v>227900</v>
+        <v>293800</v>
       </c>
       <c r="G49" s="3">
         <v>328600</v>
@@ -2488,22 +2490,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>303200</v>
+        <v>295100</v>
       </c>
       <c r="E52" s="3">
-        <v>134400</v>
+        <v>126600</v>
       </c>
       <c r="F52" s="3">
-        <v>222100</v>
+        <v>151000</v>
       </c>
       <c r="G52" s="3">
-        <v>171100</v>
+        <v>165700</v>
       </c>
       <c r="H52" s="3">
-        <v>207700</v>
+        <v>252800</v>
       </c>
       <c r="I52" s="3">
-        <v>115700</v>
+        <v>105200</v>
       </c>
       <c r="J52" s="3">
         <v>104600</v>
@@ -2706,22 +2708,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>31900</v>
+        <v>48900</v>
       </c>
       <c r="E58" s="3">
         <v>41700</v>
       </c>
       <c r="F58" s="3">
-        <v>131300</v>
+        <v>132200</v>
       </c>
       <c r="G58" s="3">
-        <v>17800</v>
+        <v>18800</v>
       </c>
       <c r="H58" s="3">
-        <v>11500</v>
+        <v>11800</v>
       </c>
       <c r="I58" s="3">
-        <v>6600</v>
+        <v>6800</v>
       </c>
       <c r="J58" s="3">
         <v>10100</v>
@@ -2751,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>420400</v>
+        <v>270400</v>
       </c>
       <c r="E59" s="3">
-        <v>368900</v>
+        <v>256300</v>
       </c>
       <c r="F59" s="3">
-        <v>349600</v>
+        <v>240800</v>
       </c>
       <c r="G59" s="3">
-        <v>344900</v>
+        <v>225800</v>
       </c>
       <c r="H59" s="3">
-        <v>316500</v>
+        <v>196700</v>
       </c>
       <c r="I59" s="3">
-        <v>331500</v>
+        <v>198900</v>
       </c>
       <c r="J59" s="3">
-        <v>282400</v>
+        <v>3000</v>
       </c>
       <c r="K59" s="3">
         <v>309300</v>
@@ -2841,22 +2843,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2147700</v>
+        <v>2199400</v>
       </c>
       <c r="E61" s="3">
         <v>1706300</v>
       </c>
       <c r="F61" s="3">
-        <v>1711600</v>
+        <v>1712300</v>
       </c>
       <c r="G61" s="3">
-        <v>1550000</v>
+        <v>1552500</v>
       </c>
       <c r="H61" s="3">
-        <v>1387400</v>
+        <v>1388600</v>
       </c>
       <c r="I61" s="3">
-        <v>1535500</v>
+        <v>1535800</v>
       </c>
       <c r="J61" s="3">
         <v>1530600</v>
@@ -2886,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>379800</v>
+        <v>73800</v>
       </c>
       <c r="E62" s="3">
-        <v>618200</v>
+        <v>140900</v>
       </c>
       <c r="F62" s="3">
-        <v>884500</v>
+        <v>210300</v>
       </c>
       <c r="G62" s="3">
-        <v>1190200</v>
+        <v>187400</v>
       </c>
       <c r="H62" s="3">
-        <v>1204800</v>
+        <v>159600</v>
       </c>
       <c r="I62" s="3">
-        <v>1137800</v>
+        <v>89100</v>
       </c>
       <c r="J62" s="3">
-        <v>1097700</v>
+        <v>73200</v>
       </c>
       <c r="K62" s="3">
         <v>1244600</v>
@@ -3066,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3612100</v>
+        <v>3504600</v>
       </c>
       <c r="E66" s="3">
-        <v>3399700</v>
+        <v>3288400</v>
       </c>
       <c r="F66" s="3">
-        <v>3599600</v>
+        <v>3452500</v>
       </c>
       <c r="G66" s="3">
-        <v>3513800</v>
+        <v>3393500</v>
       </c>
       <c r="H66" s="3">
-        <v>3544500</v>
+        <v>3441400</v>
       </c>
       <c r="I66" s="3">
-        <v>3616100</v>
+        <v>3510200</v>
       </c>
       <c r="J66" s="3">
-        <v>3446000</v>
+        <v>3340900</v>
       </c>
       <c r="K66" s="3">
         <v>3814800</v>
@@ -3313,7 +3315,7 @@
         <v>-70100</v>
       </c>
       <c r="E72" s="3">
-        <v>176900</v>
+        <v>-480900</v>
       </c>
       <c r="F72" s="3">
         <v>72700</v>
@@ -3588,10 +3590,10 @@
         <v>45291</v>
       </c>
       <c r="E80" s="2">
-        <v>44926</v>
+        <v>44927</v>
       </c>
       <c r="F80" s="2">
-        <v>44561</v>
+        <v>44563</v>
       </c>
       <c r="G80" s="2">
         <v>44196</v>
@@ -3642,7 +3644,7 @@
         <v>-1572600</v>
       </c>
       <c r="H81" s="3">
-        <v>257600</v>
+        <v>252500</v>
       </c>
       <c r="I81" s="3">
         <v>222400</v>
@@ -3694,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>146100</v>
+        <v>113600</v>
       </c>
       <c r="E83" s="3">
-        <v>142900</v>
+        <v>115400</v>
       </c>
       <c r="F83" s="3">
-        <v>143900</v>
+        <v>117400</v>
       </c>
       <c r="G83" s="3">
         <v>143300</v>
       </c>
       <c r="H83" s="3">
-        <v>151100</v>
+        <v>141100</v>
       </c>
       <c r="I83" s="3">
-        <v>156400</v>
+        <v>146400</v>
       </c>
       <c r="J83" s="3">
-        <v>160800</v>
+        <v>135200</v>
       </c>
       <c r="K83" s="3">
         <v>170300</v>
@@ -4040,7 +4042,7 @@
         <v>-136500</v>
       </c>
       <c r="H91" s="3">
-        <v>-168400</v>
+        <v>-168200</v>
       </c>
       <c r="I91" s="3">
         <v>-139200</v>
@@ -4451,26 +4453,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>ATI</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4362100</v>
+      </c>
+      <c r="E8" s="3">
         <v>4173700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3836000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2799800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2982100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4122500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4046600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3525100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3134600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3719600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4223400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4043500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4666900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4812300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3360800</v>
+        <v>3448600</v>
       </c>
       <c r="E9" s="3">
+        <v>3347400</v>
+      </c>
+      <c r="F9" s="3">
         <v>3121800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2465800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2689300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3484500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3416300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3028100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2911800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3659300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3847000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3782300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8376500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4075500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>812900</v>
+        <v>913500</v>
       </c>
       <c r="E10" s="3">
+        <v>826300</v>
+      </c>
+      <c r="F10" s="3">
         <v>714200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>334000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>292800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>638000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>630300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>497000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>222800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>60300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>376400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>261200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-3709600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>736800</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -885,25 +898,25 @@
         <v>22100</v>
       </c>
       <c r="E12" s="3">
+        <v>22100</v>
+      </c>
+      <c r="F12" s="3">
         <v>17700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>20200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14700</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,81 +981,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>18100</v>
+        <v>-46600</v>
       </c>
       <c r="E14" s="3">
+        <v>31500</v>
+      </c>
+      <c r="F14" s="3">
         <v>128000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>38300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1432900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-46100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-17200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>150900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>523800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>190900</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>67500</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>125800</v>
+      </c>
+      <c r="E15" s="3">
         <v>120600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>123400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>125400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>151300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>151100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>156400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>145200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1055,9 +1077,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3768600</v>
+        <v>3817200</v>
       </c>
       <c r="E17" s="3">
+        <v>3755200</v>
+      </c>
+      <c r="F17" s="3">
         <v>3280900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2432700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2935000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3825300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3718400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3330400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3676400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4089000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4117300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4134800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4363000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4398500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>405100</v>
+        <v>544900</v>
       </c>
       <c r="E18" s="3">
+        <v>418500</v>
+      </c>
+      <c r="F18" s="3">
         <v>555100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>367100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>47100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>297200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>328200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>194700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-541800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-369400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>106100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-91300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>303900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>413800</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-14900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>58600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>73200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>95700</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>526700</v>
+        <v>673500</v>
       </c>
       <c r="E21" s="3">
+        <v>540100</v>
+      </c>
+      <c r="F21" s="3">
         <v>693400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>494000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>196700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>440500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>487900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>343400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-312900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-176700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>288100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>101100</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>683900</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>124200</v>
+      </c>
+      <c r="E22" s="3">
         <v>105800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>92100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>97600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>96100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>104900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>102100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>134900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>250800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>111400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>109800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>66000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>144800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>187400</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>486100</v>
+      </c>
+      <c r="E23" s="3">
         <v>295200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>354600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>233400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1481900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>236500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>247700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-86500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-734000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-478000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-154800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>232300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>322100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>103400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-128200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>77700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-28500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-6800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-106900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-112100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-8700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-63600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>72400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>110400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>382700</v>
+      </c>
+      <c r="E26" s="3">
         <v>423400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>339100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>206600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1559600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>265000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>236700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-79700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-627100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-365900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-91200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>159900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>211700</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>367800</v>
+      </c>
+      <c r="E27" s="3">
         <v>410800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>323500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>184600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1572600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>252500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>222400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-91900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-640900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-377900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-98800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>150500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>202900</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1619,20 +1679,23 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>252800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>7900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>11400</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>14900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-58600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-73200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-95700</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>367800</v>
+      </c>
+      <c r="E33" s="3">
         <v>410800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>323500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>184600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1572600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>252500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>222400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-91900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-640900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-377900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>154000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>158400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>214300</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>367800</v>
+      </c>
+      <c r="E35" s="3">
         <v>410800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>323500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>184600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1572600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>252500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>222400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-91900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-640900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-377900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>154000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>158400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>214300</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,65 +2074,69 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>721200</v>
+      </c>
+      <c r="E41" s="3">
         <v>743900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>584000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>687700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>645900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>490800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>382000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>141600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>164100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>149300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>267700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1025200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>222800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>339600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -2061,217 +2150,232 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>65500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>82200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>41000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>784800</v>
+      </c>
+      <c r="E43" s="3">
         <v>684100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>643300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>523900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>384700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>592600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>579000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>545300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>452100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>603600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>528200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>613300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>709100</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1353000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1247500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1195700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1046300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>997100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1155300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1211100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1176100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1037000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1271600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1472800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1322100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1536600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1384300</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>15300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>4400</v>
       </c>
       <c r="H45" s="3">
         <v>4400</v>
       </c>
       <c r="I45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J45" s="3">
         <v>12900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>47800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>129800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>73700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>111800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>95500</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2945000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2737700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2476400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2306700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2066000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2303000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2246700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1915700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1766500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1867600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2482100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2950800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2510600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2569500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>500</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -2285,8 +2389,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2303,99 +2407,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1776900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1665900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1549100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1528500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1469200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2450100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2475000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2495700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2498900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2928200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2961800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2874100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2559900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2368800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>270900</v>
+      </c>
+      <c r="E49" s="3">
         <v>278300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>285700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>293800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>328600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>622100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>664400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>669400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>790100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>809700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>948900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>880700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>740100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>737700</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>225800</v>
+      </c>
+      <c r="E52" s="3">
         <v>295100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>126600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>151000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>165700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>252800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>105200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>104600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>114500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>146200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>189800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>192900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>802900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>370900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5230600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4985100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4445600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4285200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4034900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5634600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5501800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5185400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5170000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5751700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6582600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6898500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6247800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6046900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>609100</v>
+      </c>
+      <c r="E57" s="3">
         <v>524800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>553300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>375500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>290600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>521200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>498800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>420100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>294300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>380800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>556700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>471800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>499900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>490700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>48900</v>
+        <v>197800</v>
       </c>
       <c r="E58" s="3">
+        <v>31900</v>
+      </c>
+      <c r="F58" s="3">
         <v>41700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>132200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>105100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>419900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>17100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27300</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>270400</v>
+        <v>258100</v>
       </c>
       <c r="E59" s="3">
+        <v>294400</v>
+      </c>
+      <c r="F59" s="3">
         <v>256300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>240800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>225800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>196700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>198900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>309300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>301800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>385400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>319300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>685000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>343800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1208500</v>
+      </c>
+      <c r="E60" s="3">
         <v>977100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>963900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>856400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>653300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>849200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>836900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>712600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>708700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>686500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>959900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1211000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>871500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>861800</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2199400</v>
+        <v>1765800</v>
       </c>
       <c r="E61" s="3">
+        <v>2147700</v>
+      </c>
+      <c r="F61" s="3">
         <v>1706300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1712300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1552500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1388600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1535800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1530600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1771900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1491800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1509100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1527400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1463000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1482000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>73800</v>
+        <v>54300</v>
       </c>
       <c r="E62" s="3">
+        <v>125500</v>
+      </c>
+      <c r="F62" s="3">
         <v>140900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>210300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>187400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>159600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>89100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>73200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1244600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1376900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1392200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1165400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1436100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1131500</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3275400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3504600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3288400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3452500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3393500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3441400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3510200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3340900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3814800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3668900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3984200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4004300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3768200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3571600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-70100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-480900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>72700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>106500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1679300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1422000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1184300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1277100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1945900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2398900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2490100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2427600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2361500</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1850400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1373000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1045900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>685600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>521100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2090100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1885700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1739400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1355200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2082800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2598400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2894200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2479600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2475300</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>367800</v>
+      </c>
+      <c r="E81" s="3">
         <v>410800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>323500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>184600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1572600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>252500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>222400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-91900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-640900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-377900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>154000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>158400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>214300</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>118800</v>
+      </c>
+      <c r="E83" s="3">
         <v>113600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>115400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>117400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>143300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>141100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>146400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>135200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>170300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>189900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>176800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>189900</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>174400</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>407200</v>
+      </c>
+      <c r="E89" s="3">
         <v>85900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>224900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>166900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>230100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>392800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-43700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>131400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>55900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>368400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>427500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>296800</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-239100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-130900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-152600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-136500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-168200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-139200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-122700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-202200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-144600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-225700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-612700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-382000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-278200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-193200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-126700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-77300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-128700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>81700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-145100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-119600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-145100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-316200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-624700</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4250,26 +4483,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-25800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-66500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-77100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-76900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-76500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-74700</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,59 +4644,65 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-260400</v>
+      </c>
+      <c r="E100" s="3">
         <v>267200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-201900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>103000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>116900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-203000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>323500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-106000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-497000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>364800</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>276200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>-7600</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>8</v>
@@ -4474,8 +4722,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4486,58 +4734,64 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E102" s="3">
         <v>159900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-103700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>41800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>155100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>108800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>240400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-88000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>79800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-119700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-757300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>722200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-76000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-51700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ATI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>ATI</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
         <v>45655</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44563</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4587400</v>
+      </c>
+      <c r="E8" s="3">
         <v>4362100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4173700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3836000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2799800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2982100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4122500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4046600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3525100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3134600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3719600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4223400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4043500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4666900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4812300</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3556800</v>
+      </c>
+      <c r="E9" s="3">
         <v>3448600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3347400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3121800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2465800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2689300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3484500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3416300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3028100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2911800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3659300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3847000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3782300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8376500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4075500</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1030600</v>
+      </c>
+      <c r="E10" s="3">
         <v>913500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>826300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>714200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>334000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>292800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>638000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>630300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>497000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>222800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>60300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>376400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>261200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-3709600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>736800</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,37 +901,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>22100</v>
+        <v>23200</v>
       </c>
       <c r="E12" s="3">
         <v>22100</v>
       </c>
       <c r="F12" s="3">
+        <v>22100</v>
+      </c>
+      <c r="G12" s="3">
         <v>17700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>20200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14700</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,87 +1000,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-46600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>31500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>128000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>38300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1432900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-46100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-17200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>150900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>523800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>190900</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>67500</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>153600</v>
+      </c>
+      <c r="E15" s="3">
         <v>125800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>120600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>123400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>125400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>151300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>151100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>156400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>145200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1080,9 +1102,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3929400</v>
+      </c>
+      <c r="E17" s="3">
         <v>3817200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3755200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3280900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2432700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2935000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3825300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3718400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3330400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3676400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4089000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4117300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4134800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4363000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4398500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>658000</v>
+      </c>
+      <c r="E18" s="3">
         <v>544900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>418500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>555100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>367100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>47100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>297200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>328200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>194700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-541800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-369400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>106100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-91300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>303900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>413800</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-14900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>58600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>73200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>95700</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>815700</v>
+      </c>
+      <c r="E21" s="3">
         <v>673500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>540100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>693400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>494000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>196700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>440500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>487900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>343400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-312900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-176700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>288100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>101100</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>683900</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>110700</v>
+      </c>
+      <c r="E22" s="3">
         <v>124200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>105800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>92100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>97600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>96100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>104900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>102100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>134900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>250800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>111400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>109800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>66000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>144800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>187400</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>522300</v>
+      </c>
+      <c r="E23" s="3">
         <v>486100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>295200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>354600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>233400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1481900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>236500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>247700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-86500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-734000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-478000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-154800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>232300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>322100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>103700</v>
+      </c>
+      <c r="E24" s="3">
         <v>103400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-128200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>77700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-28500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-6800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-106900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-112100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-8700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-63600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>72400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>110400</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>418600</v>
+      </c>
+      <c r="E26" s="3">
         <v>382700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>423400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>339100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>206600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1559600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>265000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>236700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-79700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-627100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-365900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-91200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>159900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>211700</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>404300</v>
+      </c>
+      <c r="E27" s="3">
         <v>367800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>410800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>323500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>184600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1572600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>252500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>222400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-91900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-640900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-377900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-98800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>150500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>202900</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1682,20 +1742,23 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>252800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>7900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>11400</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E32" s="3">
         <v>2800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>14900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-58600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-73200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-95700</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>404300</v>
+      </c>
+      <c r="E33" s="3">
         <v>367800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>410800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>323500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>184600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1572600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>252500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>222400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-91900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-640900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-377900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>154000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>158400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>214300</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>404300</v>
+      </c>
+      <c r="E35" s="3">
         <v>367800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>410800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>323500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>184600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1572600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>252500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>222400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-91900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-640900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-377900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>154000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>158400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>214300</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
         <v>45655</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44563</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,56 +2160,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>416700</v>
+      </c>
+      <c r="E41" s="3">
         <v>721200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>743900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>584000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>687700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>645900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>490800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>382000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>141600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>164100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>149300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>267700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1025200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>222800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>339600</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2132,14 +2221,14 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2153,218 +2242,233 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>65500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>82200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>41000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>758900</v>
+      </c>
+      <c r="E43" s="3">
         <v>784800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>684100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>643300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>523900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>384700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>592600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>579000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>545300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>452100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>603600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>528200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>613300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>709100</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1403200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1353000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1247500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1195700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1046300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>997100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1155300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1211100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1176100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1037000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1271600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1472800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1322100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1536600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1384300</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>4400</v>
       </c>
       <c r="I45" s="3">
         <v>4400</v>
       </c>
       <c r="J45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K45" s="3">
         <v>12900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>47800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>45500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>129800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>73700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>111800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>95500</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2680000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2945000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2737700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2476400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2306700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2066000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2303000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2246700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1915700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1766500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1867600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2482100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2950800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2510600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2569500</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2374,11 +2478,11 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>500</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -2392,8 +2496,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2410,105 +2514,114 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1940600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1776900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1665900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1549100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1528500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1469200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2450100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2475000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2495700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2498900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2928200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2961800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2874100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2559900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2368800</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>261100</v>
+      </c>
+      <c r="E49" s="3">
         <v>270900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>278300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>285700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>293800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>328600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>622100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>664400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>669400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>790100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>809700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>948900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>880700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>740100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>737700</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>202300</v>
+      </c>
+      <c r="E52" s="3">
         <v>225800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>295100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>126600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>151000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>165700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>252800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>105200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>104600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>114500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>146200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>189800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>192900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>802900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>370900</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5099600</v>
+      </c>
+      <c r="E54" s="3">
         <v>5230600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4985100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4445600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4285200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4034900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5634600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5501800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5185400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5170000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5751700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6582600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6898500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6247800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6046900</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>568200</v>
+      </c>
+      <c r="E57" s="3">
         <v>609100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>524800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>553300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>375500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>290600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>521200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>498800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>420100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>294300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>380800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>556700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>471800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>499900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>490700</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>197800</v>
+        <v>53400</v>
       </c>
       <c r="E58" s="3">
+        <v>180400</v>
+      </c>
+      <c r="F58" s="3">
         <v>31900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>41700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>132200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>105100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>17800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>419900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>17100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>258100</v>
+        <v>231400</v>
       </c>
       <c r="E59" s="3">
+        <v>281500</v>
+      </c>
+      <c r="F59" s="3">
         <v>294400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>256300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>240800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>225800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>196700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>198900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>309300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>301800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>385400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>319300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>685000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>343800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1006300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1208500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>977100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>963900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>856400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>653300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>849200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>836900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>712600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>708700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>686500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>959900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1211000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>871500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>861800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1765800</v>
+        <v>1785000</v>
       </c>
       <c r="E61" s="3">
+        <v>1714900</v>
+      </c>
+      <c r="F61" s="3">
         <v>2147700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1706300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1712300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1552500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1388600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1535800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1530600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1771900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1491800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1509100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1527400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1463000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1482000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>54300</v>
+        <v>100400</v>
       </c>
       <c r="E62" s="3">
+        <v>105200</v>
+      </c>
+      <c r="F62" s="3">
         <v>125500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>140900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>210300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>187400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>159600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>89100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>73200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1244600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1376900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1392200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1165400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1436100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1131500</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3182900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3275400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3504600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3288400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3452500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3393500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3441400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3510200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3340900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3814800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3668900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3984200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4004300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3768200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3571600</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>468700</v>
+      </c>
+      <c r="E72" s="3">
         <v>64300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-70100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-480900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>72700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>106500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1679300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1422000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1184300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1277100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1945900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2398900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2490100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2427600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2361500</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1804500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1850400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1373000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1045900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>685600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>521100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2090100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1885700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1739400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1355200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2082800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2598400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2894200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2479600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2475300</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
         <v>45655</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44563</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>404300</v>
+      </c>
+      <c r="E81" s="3">
         <v>367800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>410800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>323500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>184600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1572600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>252500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>222400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-91900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-640900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-377900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>154000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>158400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>214300</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E83" s="3">
         <v>118800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>113600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>115400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>117400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>143300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>141100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>146400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>135200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>170300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>189900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>176800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>189900</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>174400</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>614300</v>
+      </c>
+      <c r="E89" s="3">
         <v>407200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>85900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>224900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>166900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>230100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>392800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-43700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>131400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>55900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>368400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>427500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>296800</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-280600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-239100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-130900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-152600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-136500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-168200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-139200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-122700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-202200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-144600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-225700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-612700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-382000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-278200</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-234500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-159600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-193200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-126700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-128700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>81700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-145100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-119600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-145100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-316200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11000</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-624700</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,8 +4688,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4486,26 +4719,29 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-25800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-66500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-77100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-76900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-76500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-74700</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,65 +4889,71 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-699900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-260400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>267200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-201900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>103000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>116900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-203000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>323500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-106000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-497000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>364800</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>276200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7600</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>8</v>
@@ -4725,8 +4973,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4737,61 +4985,67 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-304500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-20400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>159900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-103700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>41800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>155100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>108800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>240400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-88000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>79800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-119700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-757300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>722200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-76000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-51700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
